--- a/verification/cases/roundtrip/scatter_chart/init.xlsx
+++ b/verification/cases/roundtrip/scatter_chart/init.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onealj\Downloads\poi\test-data\spreadsheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{245FC15C-4286-4201-93A8-9DD8633FEDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15330" windowHeight="6840"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -86,7 +87,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -100,7 +101,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -203,6 +203,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0782-4369-9E16-BE2EE9113A6D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -349,7 +354,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -417,7 +421,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -431,7 +435,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -534,6 +537,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6EEA-4E3C-B1F4-EF484FBE3D72}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -680,7 +688,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1855,7 +1862,7 @@
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1879,7 +1886,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1904,7 +1917,13 @@
     <xdr:ext cx="8676680" cy="6280547"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks noGrp="1"/>
         </xdr:cNvGraphicFramePr>
@@ -2186,11 +2205,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2198,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2206,7 +2225,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
